--- a/results/Int All Data -0.4/Rando_fi_explain.xlsx
+++ b/results/Int All Data -0.4/Rando_fi_explain.xlsx
@@ -1676,466 +1676,466 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001054538151491634</v>
+        <v>-0.0001004266514509376</v>
       </c>
       <c r="C3" t="n">
-        <v>4.180088556002605e-05</v>
+        <v>-0.0005098665373163903</v>
       </c>
       <c r="D3" t="n">
-        <v>3.839362232936678e-05</v>
+        <v>-1.089109194499343e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001116159625395969</v>
+        <v>0.0001882738353149205</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001150201006187635</v>
+        <v>0.0002405582373682802</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001145847499029046</v>
+        <v>0.0003186256366329454</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0006257082099795486</v>
+        <v>0.0001309364430006255</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0008449627862482644</v>
+        <v>0.0008483735525882318</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.000524289861873697</v>
+        <v>0.0008910584290180157</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0002014936199257822</v>
+        <v>-0.0002486994406375731</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0001285303536525018</v>
+        <v>-0.0005114039911029899</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0001726568520364646</v>
+        <v>0.000737802755215139</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.000711857416318038</v>
+        <v>-0.0005718692232633008</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0004599806761844039</v>
+        <v>-0.0005654171666328832</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0004384761466764341</v>
+        <v>0.0002609576746812247</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001847352511406679</v>
+        <v>0.001175506551302047</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.0004195684761977149</v>
+        <v>-0.001284829800994652</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0008147575452492039</v>
+        <v>0.0005221176120321003</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0001426216238366496</v>
+        <v>-0.0004692418851257784</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0005653999591135649</v>
+        <v>0.0004435963781828456</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0009384904561556074</v>
+        <v>-0.0005036775378376036</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0004543648921352227</v>
+        <v>0.0005221391944120724</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0005963847919671194</v>
+        <v>-0.0004335426916464613</v>
       </c>
       <c r="Y3" t="n">
-        <v>-9.431657446587138e-05</v>
+        <v>7.002440661984408e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0009563389117562859</v>
+        <v>-0.0007788614758045154</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001289974484037592</v>
+        <v>0.001530782975797413</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.695119333520959e-05</v>
+        <v>-1.505631333678314e-05</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.0003416935158650258</v>
+        <v>-3.69126212478465e-05</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.003972824894321299</v>
+        <v>0.002038680902379545</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.007331704031743966</v>
+        <v>0.003695147725746011</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.00137077992907013</v>
+        <v>-0.0009306085343897432</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.000154345079588648</v>
+        <v>4.868813788330142e-06</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0001044728133571126</v>
+        <v>-0.0001521077619595801</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.0005955677849767005</v>
+        <v>0.0004820003294732543</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.001686522299567029</v>
+        <v>0.002545998211593383</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.01036313168642031</v>
+        <v>0.01026221327643844</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.000172359159545894</v>
+        <v>-0.000476433076135725</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.0008080324055330691</v>
+        <v>0.0004339710355631564</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.001076286107303511</v>
+        <v>-2.653531944364129e-05</v>
       </c>
       <c r="AO3" t="n">
-        <v>-9.420092814123011e-06</v>
+        <v>-0.0002068922279379272</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.0004388977685933493</v>
+        <v>8.066079787968138e-05</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.0006266852914245202</v>
+        <v>-0.0009918633009630673</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.004336026738255211</v>
+        <v>0.00545536346058795</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.0005773123149555969</v>
+        <v>-0.0001212895274486792</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.0001945774324372363</v>
+        <v>6.779200085366039e-05</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.000689338546122622</v>
+        <v>-0.0007239216154533691</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.0005205276332028219</v>
+        <v>-0.0006112687126464345</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.0002288199384907919</v>
+        <v>-0.0004804018316213798</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.275704872496067e-05</v>
+        <v>-4.858567980307372e-05</v>
       </c>
       <c r="AY3" t="n">
-        <v>6.592024917082546e-05</v>
+        <v>0.0001773246213319045</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.001323566663912657</v>
+        <v>0.0001995970381760614</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.002366407409931851</v>
+        <v>0.001292381399405666</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.001680924524627291</v>
+        <v>0.0004362655929625902</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.000371374021309665</v>
+        <v>-7.55913298934241e-05</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.0002049503436269262</v>
+        <v>-0.0001485993355460136</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.0001119663946981498</v>
+        <v>-5.213917876005125e-05</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.002310666203145378</v>
+        <v>-0.0001559778860856108</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.001252070465838217</v>
+        <v>0.0002385044942295267</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0.0001568732404615936</v>
+        <v>0.0003315869779526348</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.003455190367931192</v>
+        <v>0.003032712104335472</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.001681365914071079</v>
+        <v>7.067907303897944e-05</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.0004293377340335668</v>
+        <v>-0.0008629330674119883</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.0004982070999174859</v>
+        <v>-2.544496770118265e-06</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.0005907674712065959</v>
+        <v>0.0001098230527324507</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.001702982348676287</v>
+        <v>0.001971833157318208</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.001757338350449788</v>
+        <v>0.0005126970258724217</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.0004857925022496634</v>
+        <v>-0.0003490650180778276</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.001751928012721243</v>
+        <v>0.001627606115255831</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.0007640334552332373</v>
+        <v>-0.0002535072250252624</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.0001228402038330212</v>
+        <v>0.0003470666125507371</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.001604160362182807</v>
+        <v>0.001838316970070399</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.0008592983696425315</v>
+        <v>1.362349628509567e-05</v>
       </c>
       <c r="BW3" t="n">
-        <v>-3.777036159297586e-05</v>
+        <v>8.351855381367739e-06</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.0003153824067652987</v>
+        <v>-0.0002469856206217834</v>
       </c>
       <c r="BY3" t="n">
-        <v>-9.29795491211638e-05</v>
+        <v>-0.0004962576687711951</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.0001139355468713166</v>
+        <v>0.0003689505144446748</v>
       </c>
       <c r="CA3" t="n">
-        <v>-0.0001215046421968113</v>
+        <v>-0.0002141140526056351</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0.0003623833904429164</v>
+        <v>-0.0008094110742405215</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.0009853883513546201</v>
+        <v>-0.0007615392402235699</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.865528578388556e-06</v>
+        <v>-0.0008947791387368577</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.001223784291640775</v>
+        <v>-0.001212501130568155</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.082855093159086e-05</v>
+        <v>-0.0002311890242166614</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.0001816214066773303</v>
+        <v>-0.0006620221588044108</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.000134170418649725</v>
+        <v>-0.0003337407148297678</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.0006711199638655518</v>
+        <v>0.000194435426720556</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-4.893905841961921e-05</v>
+        <v>-6.281397247080993e-06</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.001031496656076923</v>
+        <v>-0.0008582838836513707</v>
       </c>
       <c r="CL3" t="n">
-        <v>-0.0009436043089852486</v>
+        <v>-0.001617270381898897</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.0003223138458726472</v>
+        <v>-5.735186387725525e-05</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.0002755034655588397</v>
+        <v>0.000225297654933132</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.000501947610198422</v>
+        <v>0.0009066057390180127</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.0001556021202086366</v>
+        <v>-8.121921660778077e-05</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.001955073415157112</v>
+        <v>0.0001619785431118049</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.001091072550731145</v>
+        <v>-0.002747219715591687</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0.00146111500083394</v>
+        <v>-0.002002342528792754</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0.0006816431635052899</v>
+        <v>-0.001567282802941377</v>
       </c>
       <c r="CU3" t="n">
-        <v>-5.833057920102703e-06</v>
+        <v>-0.0001450491973471479</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0.0001648987397347501</v>
+        <v>6.793113031075437e-05</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.00192725136502468</v>
+        <v>-0.00227648337290291</v>
       </c>
       <c r="CY3" t="n">
-        <v>-0.001762399764373657</v>
+        <v>-0.00334087251708165</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.0001878658242113506</v>
+        <v>-0.0002073734435469953</v>
       </c>
       <c r="DA3" t="n">
-        <v>-0.0001767042924020779</v>
+        <v>0.0002055052212230402</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.0005746157869743563</v>
+        <v>0.0004156668969801492</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0.001832727416318156</v>
+        <v>-0.003792950152902728</v>
       </c>
       <c r="DD3" t="n">
-        <v>-9.963714628506758e-05</v>
+        <v>-0.0003497942124261011</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.001139099749277269</v>
+        <v>0.000536237201295835</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.001587212623795132</v>
+        <v>-0.001985070227504291</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.000481665720790948</v>
+        <v>0.000476079906935426</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.0002080888645285106</v>
+        <v>-0.0008957667174212324</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.0003022371209366526</v>
+        <v>0.0003219758040731424</v>
       </c>
       <c r="DJ3" t="n">
-        <v>9.494216938742538e-05</v>
+        <v>-0.000409603908584062</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0.0008783082115813836</v>
+        <v>-0.0005690139650607695</v>
       </c>
       <c r="DL3" t="n">
-        <v>5.665743437315407e-05</v>
+        <v>-8.462201098710987e-05</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.0004375318588514353</v>
+        <v>-0.0004495270357762005</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.0008627083050557503</v>
+        <v>-0.002409648129718642</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.0003531065440222004</v>
+        <v>-0.001979363098574534</v>
       </c>
       <c r="DP3" t="n">
-        <v>1.152112941521405e-05</v>
+        <v>-0.001768257867134394</v>
       </c>
       <c r="DQ3" t="n">
-        <v>6.634719904912044e-05</v>
+        <v>-7.223578095614801e-05</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.0001434071282706406</v>
+        <v>-0.0001170236655962864</v>
       </c>
       <c r="DS3" t="n">
-        <v>1.398951699123853e-05</v>
+        <v>-6.565521330449404e-06</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0.0003698382675696588</v>
+        <v>0.0002003394076332187</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.0001707674795211757</v>
+        <v>-0.001018908239861067</v>
       </c>
       <c r="DV3" t="n">
-        <v>-6.285355122563897e-06</v>
+        <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.0001230543300143816</v>
+        <v>2.9382889855889e-05</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.000171113295654225</v>
+        <v>-0.000348803424384283</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.0002533413394168461</v>
+        <v>-0.001570945802363474</v>
       </c>
       <c r="DZ3" t="n">
-        <v>-3.15626135147351e-05</v>
+        <v>0.000119131903933537</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.0006106242864555155</v>
+        <v>-0.001012025840557038</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.0001917017350068196</v>
+        <v>-0.002188712464198858</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0.0002064894705611187</v>
+        <v>-0.0009458103806626527</v>
       </c>
       <c r="ED3" t="n">
-        <v>-0.0002379682238071435</v>
+        <v>-0.0004960947355922895</v>
       </c>
       <c r="EE3" t="n">
-        <v>-5.388079964974034e-05</v>
+        <v>-8.125232924593993e-06</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.0004207345291551922</v>
+        <v>-0.000232596806379598</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.0001836259893804881</v>
+        <v>-0.0005723531653153203</v>
       </c>
       <c r="EH3" t="n">
-        <v>1.09617830171227e-05</v>
+        <v>3.600206558808994e-05</v>
       </c>
       <c r="EI3" t="n">
-        <v>4.69327082049087e-05</v>
+        <v>0.0004174370285643126</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.0004933472533432548</v>
+        <v>-0.0001058577520759763</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0.0005061135275184648</v>
+        <v>-0.0001033909585702331</v>
       </c>
       <c r="EL3" t="n">
-        <v>-3.497869122470853e-05</v>
+        <v>2.339132120464104e-05</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.0001716795392605386</v>
+        <v>5.31022387726099e-05</v>
       </c>
       <c r="EN3" t="n">
-        <v>3.678825180897242e-06</v>
+        <v>-3.392312735310817e-06</v>
       </c>
       <c r="EO3" t="n">
         <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.0001440081200904441</v>
+        <v>6.763673939531143e-05</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.0004504349728683932</v>
+        <v>-0.0005805624505422057</v>
       </c>
       <c r="ER3" t="n">
-        <v>-4.182224145206859e-05</v>
+        <v>5.971011304981344e-05</v>
       </c>
       <c r="ES3" t="n">
-        <v>-1.197932500788701e-05</v>
+        <v>-9.658066043020218e-05</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0.0003167616585781008</v>
+        <v>-2.129271921846976e-05</v>
       </c>
       <c r="EU3" t="n">
-        <v>-0.0007178392256091005</v>
+        <v>-5.16841892871334e-05</v>
       </c>
       <c r="EV3" t="n">
-        <v>5.889540889221335e-05</v>
+        <v>0.000187064179391776</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.0001413683181572389</v>
+        <v>-0.0001851147249012508</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.0002654587223583438</v>
+        <v>-0.0008561926005266785</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.0007329241973835398</v>
+        <v>-0.0006858389452689484</v>
       </c>
     </row>
     <row r="4">
@@ -2145,466 +2145,466 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003730774676167916</v>
+        <v>0.002701921874523042</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001469831432212071</v>
+        <v>0.001642271529888718</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001310061307024513</v>
+        <v>0.001343949868105148</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001599099027471311</v>
+        <v>0.001384903614332314</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00109847728938682</v>
+        <v>0.0007910804167634515</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001969644516136912</v>
+        <v>0.001599747765284516</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0025667271110968</v>
+        <v>0.001647064821230201</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005755723213975441</v>
+        <v>0.001983790085134754</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002906767350437557</v>
+        <v>0.002107783887107798</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0008150294310812585</v>
+        <v>0.0006777560732864264</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006091385124064516</v>
+        <v>0.0009627416915648742</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002314676361662765</v>
+        <v>0.002056360201381513</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007297335269990474</v>
+        <v>0.009627208086272643</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003893329676146861</v>
+        <v>0.003250364962112479</v>
       </c>
       <c r="P4" t="n">
-        <v>0.00123776553910164</v>
+        <v>0.001418082097516686</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.006986664367713596</v>
+        <v>0.006394750403978781</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002906661812714054</v>
+        <v>0.0009869286477811176</v>
       </c>
       <c r="S4" t="n">
-        <v>0.00476340492535635</v>
+        <v>0.003157020150192167</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001297226668823947</v>
+        <v>0.0006252875850899871</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002318988459480207</v>
+        <v>0.001055891125460984</v>
       </c>
       <c r="V4" t="n">
-        <v>0.005385578105179382</v>
+        <v>0.002523618176921141</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001318132862177408</v>
+        <v>0.001729708235981865</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002518946989398573</v>
+        <v>0.003280776283139818</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001023060466573904</v>
+        <v>0.0004356577916139768</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002862785635509512</v>
+        <v>0.003630917808677552</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.006896387080594688</v>
+        <v>0.004890106592719732</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.000604246965134739</v>
+        <v>0.0008414437042522718</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.003537470293138778</v>
+        <v>0.002249354146203971</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.007135424595086495</v>
+        <v>0.004853434353283313</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.006397072607342114</v>
+        <v>0.006943689944660903</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.004446341352645262</v>
+        <v>0.003576974536297768</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001512669626228977</v>
+        <v>0.001106146764527748</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.001308042674667758</v>
+        <v>0.0008845727831030076</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.001129260931389805</v>
+        <v>0.003240318198500639</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.006142572029099009</v>
+        <v>0.005006392905178399</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.008773647468757763</v>
+        <v>0.007755156255084803</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.001045508695119031</v>
+        <v>0.001478673126606937</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.006282677098196372</v>
+        <v>0.00713310851340577</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.002606509920934758</v>
+        <v>0.001720685910193727</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.003550035788716776</v>
+        <v>0.003606379891064186</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.001548411146943185</v>
+        <v>0.0017305114817732</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.002570488948146426</v>
+        <v>0.002829193900970718</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.005526187241304207</v>
+        <v>0.007619962526311351</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.001510178911260263</v>
+        <v>0.001683189350306061</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.003531605956502388</v>
+        <v>0.002115964100213405</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.001871826270068306</v>
+        <v>0.001714138950054242</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.001154844390652427</v>
+        <v>0.001304486162267909</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.002900014299743188</v>
+        <v>0.002862206245389067</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0007947754555429162</v>
+        <v>0.0006974356889092503</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.002579420940888484</v>
+        <v>0.001475046862060033</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.003850193202132766</v>
+        <v>0.0008496889920242094</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.004493166496121464</v>
+        <v>0.004094642765597208</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.005778444033565557</v>
+        <v>0.005331807891664056</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0005364632314160729</v>
+        <v>0.0006443464206543205</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0006101548277013501</v>
+        <v>0.0005814834764984833</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.002249172282351937</v>
+        <v>0.001910422412693569</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.00341384937319324</v>
+        <v>0.00416927286300847</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.005441874790632913</v>
+        <v>0.003840339836230992</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.001184055586656221</v>
+        <v>0.001263823066203582</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.006404780784909136</v>
+        <v>0.006141479986430803</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.00331919035917145</v>
+        <v>0.002551514415326239</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.003555784182575723</v>
+        <v>0.003105393498564668</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0008885722550598316</v>
+        <v>0.0004158939326151856</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.0008417350319040719</v>
+        <v>0.001194010131569967</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.002978798824798337</v>
+        <v>0.003156722007728893</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.002093903034384676</v>
+        <v>0.003744304774847526</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.002198297471667294</v>
+        <v>0.002581859643302914</v>
       </c>
       <c r="BQ4" t="n">
         <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.003510293850972139</v>
+        <v>0.00319996898031859</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.001719506612622941</v>
+        <v>0.001476937953862034</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.001924939321175014</v>
+        <v>0.0009660191603683407</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.001964631974220511</v>
+        <v>0.00305925088964554</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.001875829106086852</v>
+        <v>0.00127203945502564</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0002071195614642709</v>
+        <v>9.600771211388195e-05</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.002646162126139435</v>
+        <v>0.002842631989668227</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.001735990226278085</v>
+        <v>0.00236126060461491</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.004219462416841232</v>
+        <v>0.002733012848133372</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.001653662611930437</v>
+        <v>0.0008440419983149938</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.003641786797825628</v>
+        <v>0.003625765467048926</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.001658724360101842</v>
+        <v>0.002406838931281521</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.002925114056510063</v>
+        <v>0.003124446951602169</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.004204699038192033</v>
+        <v>0.002390928091806981</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.002467423857829023</v>
+        <v>0.001620596671184761</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.002350494647471256</v>
+        <v>0.0019750018066279</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0007384697380542618</v>
+        <v>0.001031217300217061</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.002733302614227387</v>
+        <v>0.002224284832103113</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0001229415316969516</v>
+        <v>0.0002416753644077681</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.002084486984531131</v>
+        <v>0.00163557347682489</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.003224928841960885</v>
+        <v>0.003743428901835278</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.001711227337645951</v>
+        <v>0.001895815922663982</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.001958558415996399</v>
+        <v>0.001519486293296783</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.002015423266951764</v>
+        <v>0.002208475378222954</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.0002198701695723264</v>
+        <v>0.0003727390318125132</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.003171685575357628</v>
+        <v>0.002464567832081565</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.006587553777260258</v>
+        <v>0.00625599807798283</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.003219747785655911</v>
+        <v>0.003857084785023874</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.001778768749789923</v>
+        <v>0.002564778676056799</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0006703504122622829</v>
+        <v>0.0002985240598880966</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0004014361870108812</v>
+        <v>0.0001158584958973424</v>
       </c>
       <c r="CW4" t="n">
         <v>0</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.004217111311338062</v>
+        <v>0.003528572802492245</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.005244470703298527</v>
+        <v>0.006738572534307416</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0001946414668569512</v>
+        <v>0.0005614695378943008</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0006644694234034529</v>
+        <v>0.0003583537071277683</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.003139491438925403</v>
+        <v>0.003921381990857913</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.005034457525704143</v>
+        <v>0.005395455572909168</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.0004592145262083118</v>
+        <v>0.0004076014658693338</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.001671149913319678</v>
+        <v>0.002286513901387665</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.005200516686766299</v>
+        <v>0.005100281248405355</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.001411881629649679</v>
+        <v>0.0008497749398611178</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.004001991972207904</v>
+        <v>0.002161804565733671</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.001619875022423775</v>
+        <v>0.001624281388358625</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.003552882218126474</v>
+        <v>0.002148549377426014</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.004993379186427604</v>
+        <v>0.001362543597021051</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.000330604769407447</v>
+        <v>0.0002440018113535283</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.001787899648165734</v>
+        <v>0.001481298765186433</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.005389513647400881</v>
+        <v>0.004018508610269869</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.004849188867209694</v>
+        <v>0.003111564055615069</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.00247136946805306</v>
+        <v>0.002273705610998412</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0004604391816285475</v>
+        <v>0.0002589742980552273</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0005652625874973987</v>
+        <v>0.0004354132159190496</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0005133462565359364</v>
+        <v>0.0003583372509149328</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.001914103064546712</v>
+        <v>0.001929561361075328</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.003050587990269079</v>
+        <v>0.00279117103541178</v>
       </c>
       <c r="DV4" t="n">
-        <v>1.98760380903087e-05</v>
+        <v>0</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0004984229363458819</v>
+        <v>0.0003635190678007483</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.001328612862481121</v>
+        <v>0.001339098118817181</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.006015048230504347</v>
+        <v>0.002785006063522083</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0003738158183738942</v>
+        <v>0.0003735520540939622</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.001500173599547909</v>
+        <v>0.003185210347403077</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.002680668790280435</v>
+        <v>0.001660310673330345</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.0007489689146336016</v>
+        <v>0.001155512658193047</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.001567995294044026</v>
+        <v>0.0009590055571241806</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0001203573378194106</v>
+        <v>9.846003456382599e-05</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.001296856161877771</v>
+        <v>0.001132783797505026</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.001519775883835723</v>
+        <v>0.001986267040877319</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0006370823700666181</v>
+        <v>0.000564321520629851</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.001828449088052463</v>
+        <v>0.0007232039721442598</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.001316662014446938</v>
+        <v>0.001381790473793244</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.003037998362978183</v>
+        <v>0.001165726745534194</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.0001010645703612793</v>
+        <v>9.935384536646122e-05</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0005147146590881002</v>
+        <v>9.333725394717613e-05</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0003408653924287094</v>
+        <v>0.000297052930703153</v>
       </c>
       <c r="EO4" t="n">
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.0004079043486942861</v>
+        <v>0.0004611161978251447</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.002049768499540087</v>
+        <v>0.0004477395085818156</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.0001430334486413141</v>
+        <v>0.0002112576276018512</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.000220524720464805</v>
+        <v>0.0004615141468368045</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.001413616856299163</v>
+        <v>0.0006119225022987307</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.001651653314672342</v>
+        <v>0.001398068956397458</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.0002177610574920356</v>
+        <v>0.0003459942482383101</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.001463935224454444</v>
+        <v>0.0006851275428724274</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.001929987559480636</v>
+        <v>0.001827279027590585</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.001997861832075383</v>
+        <v>0.00156137615786318</v>
       </c>
     </row>
     <row r="5">
@@ -2614,466 +2614,466 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.005245294662141376</v>
+        <v>-0.00439068100358424</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.00342486886763349</v>
+        <v>-0.005022692889561309</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.001912989817957445</v>
+        <v>-0.002177246243483544</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0009612303748798623</v>
+        <v>-0.001345722524831816</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.002498418722327689</v>
+        <v>-0.000562148657089323</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0009856630824372937</v>
+        <v>-0.001865907653383958</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.002962048750385737</v>
+        <v>-0.003488372093023284</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01616784942918856</v>
+        <v>-0.001344086021505431</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.006263498920086452</v>
+        <v>-0.002637227844219525</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.001463560334528136</v>
+        <v>-0.001602050624799789</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.001265022137887462</v>
+        <v>-0.00224287087471966</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.005439595192915936</v>
+        <v>-0.002116244411326373</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01308238198087015</v>
+        <v>-0.0220610922554767</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.009904350509102178</v>
+        <v>-0.007713668620796055</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.001482602118003007</v>
+        <v>-0.001635444543562326</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.01105414931111821</v>
+        <v>-0.007147375079063889</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.007004011107682862</v>
+        <v>-0.002692889561270828</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.01012033323048447</v>
+        <v>-0.003657448706512079</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.002081474873624778</v>
+        <v>-0.001634091637295765</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.003856834310398072</v>
+        <v>-0.001481024375192863</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.01363776612156747</v>
+        <v>-0.004072817031780307</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.0009291893623838531</v>
+        <v>-0.002087286527514254</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.005218216318785629</v>
+        <v>-0.00600885515496521</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.002277039848197393</v>
+        <v>-0.000771366862079581</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.003542061986084821</v>
+        <v>-0.005047789725209095</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.009139784946236584</v>
+        <v>-0.004048070841239737</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.000863930885529196</v>
+        <v>-0.001992409867172695</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.004743833017077858</v>
+        <v>-0.00433094384707291</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.005918429929469471</v>
+        <v>-0.006293485135989885</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.001349279362158873</v>
+        <v>-0.005083207261724687</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.004293495674463299</v>
+        <v>-0.009580262736302515</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.002114706824735657</v>
+        <v>-0.001043643263757121</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.002018583787247674</v>
+        <v>-0.001374141161773901</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.001707779886148064</v>
+        <v>-0.006419987349778622</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.005939660590823392</v>
+        <v>-0.003136200716845894</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.003315412186379962</v>
+        <v>-0.002182163187855812</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.002146050670640798</v>
+        <v>-0.00348733233979136</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.006913890634820874</v>
+        <v>-0.005439595192915881</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.00709657513113241</v>
+        <v>-0.003447185325743207</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.006578115117014604</v>
+        <v>-0.007108721624850678</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.002846299810246733</v>
+        <v>-0.002545568824638644</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.005495818399044239</v>
+        <v>-0.004165331624479374</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.00458186478692727</v>
+        <v>-0.004712207463630625</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.001436602123672714</v>
+        <v>-0.002837514934289143</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.007096575131132399</v>
+        <v>-0.003029356652092463</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.0018026565464896</v>
+        <v>-0.004237824161922832</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.003207261724659538</v>
+        <v>-0.003941044537007421</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.003494623655914009</v>
+        <v>-0.005537065052950129</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.001512859304084702</v>
+        <v>-0.001073290401717231</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.002449223416965407</v>
+        <v>-0.001694402420574903</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.00394939833384762</v>
+        <v>-0.001057353412367856</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.003542061986084799</v>
+        <v>-0.003668564199873514</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.007969639468690748</v>
+        <v>-0.009550917141049987</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.0002846299810247199</v>
+        <v>-0.0007906388361796357</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.0003456945317410698</v>
+        <v>-0.001073290401717197</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.003865596193874565</v>
+        <v>-0.003649187365838647</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.003865493400377129</v>
+        <v>-0.007636706473915789</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.01613699475470539</v>
+        <v>-0.00755939524838013</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.002563338301043172</v>
+        <v>-0.001546238477549844</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.004581864786927248</v>
+        <v>-0.003853046594982102</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.001581277672359305</v>
+        <v>-0.003447185325743196</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.007466831224930637</v>
+        <v>-0.00477897252090802</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.0004085480829666976</v>
+        <v>-0.0006957621758380883</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.0007049022749118672</v>
+        <v>-0.002011313639220635</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.002719797596457996</v>
+        <v>-0.002036408515890176</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.001477058453802638</v>
+        <v>-0.003640851589015737</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.003289057558507336</v>
+        <v>-0.005376344086021534</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.003636938646426357</v>
+        <v>-0.002055660974067053</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.001602765556253949</v>
+        <v>-0.00385304659498209</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.00435050910212903</v>
+        <v>-0.0008623253047874146</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.001234186979327423</v>
+        <v>-0.00219068188830609</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.002270011947431316</v>
+        <v>-0.001929158760278293</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.0005553841406974013</v>
+        <v>-9.487666034156961e-05</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.004775458570525049</v>
+        <v>-0.004617330803289066</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.002531239987183598</v>
+        <v>-0.004689910521444018</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.004645946811919243</v>
+        <v>-0.005675029868578263</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.004002389486260494</v>
+        <v>-0.001802656546489567</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.005337858685590902</v>
+        <v>-0.009993674889310578</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.0005376344086021722</v>
+        <v>-0.005227001194743142</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.006728612624158914</v>
+        <v>-0.007465555911566846</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.004395951929158803</v>
+        <v>-0.004934003771213102</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.005316606929510193</v>
+        <v>-0.002624920936116382</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.006063321385902065</v>
+        <v>-0.00415173237753883</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.001210287443267755</v>
+        <v>-0.002867383512544819</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.006198608475648381</v>
+        <v>-0.003614097968936703</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.0002682563338300858</v>
+        <v>-0.000302571860816947</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.001954501762255678</v>
+        <v>-0.004453700736943322</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0.008183990442054978</v>
+        <v>-0.008917000925640239</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0.001533272002453212</v>
+        <v>-0.002777777777777801</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.00179211469534053</v>
+        <v>-0.001634091637295765</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0.002595322012175561</v>
+        <v>-0.002419354838709697</v>
       </c>
       <c r="CP5" t="n">
-        <v>-9.25640234495928e-05</v>
+        <v>-0.0005973715651135247</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.001249599487343789</v>
+        <v>-0.002979814162127559</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.01215651135005975</v>
+        <v>-0.01396988144825381</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.007437275985663105</v>
+        <v>-0.008930704898446861</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0.004301075268817245</v>
+        <v>-0.007646356033452828</v>
       </c>
       <c r="CU5" t="n">
-        <v>-0.001644528779253673</v>
+        <v>-0.0006869772998805534</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0.0007731192387749663</v>
+        <v>-6.17093489663656e-05</v>
       </c>
       <c r="CW5" t="n">
         <v>0</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0.01302270011947434</v>
+        <v>-0.01021505376344089</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0.01227598566308246</v>
+        <v>-0.01335125448028676</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.0001542733724159584</v>
+        <v>-0.001121435437359841</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0.001698173662287739</v>
+        <v>-0.0002563280999680062</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0.004069208586991358</v>
+        <v>-0.005543095161807165</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0.01305256869772999</v>
+        <v>-0.01493428912783754</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0.0007866868381240621</v>
+        <v>-0.001138519924098669</v>
       </c>
       <c r="DE5" t="n">
-        <v>-0.001537968599807749</v>
+        <v>-0.003046594982078888</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.01565113500597375</v>
+        <v>-0.01556152927120672</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0.0009932713873758159</v>
+        <v>-0.0003285543608124386</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0.004931921331316124</v>
+        <v>-0.004142947501581273</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.002602118003025655</v>
+        <v>-0.001170145477545859</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0.009773071104387276</v>
+        <v>-0.006051437216338917</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0.01461422087745833</v>
+        <v>-0.00302571860816947</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0.000695915279878978</v>
+        <v>-0.0004769001490313229</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0.002269288956127003</v>
+        <v>-0.002755527074655606</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0.009076533839342215</v>
+        <v>-0.01147077309868011</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.01271347248576853</v>
+        <v>-0.006736242884250465</v>
       </c>
       <c r="DP5" t="n">
-        <v>-0.004459203036053183</v>
+        <v>-0.006656580937972767</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.0006325110689437974</v>
+        <v>-0.0007590132827324569</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.000462820117247853</v>
+        <v>-0.001318613922109746</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.001131363922061612</v>
+        <v>-0.0005446293494705045</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0.003661119515884948</v>
+        <v>-0.002390317700453881</v>
       </c>
       <c r="DU5" t="n">
-        <v>-0.007084123972169542</v>
+        <v>-0.006631049654305466</v>
       </c>
       <c r="DV5" t="n">
-        <v>-6.285355122563896e-05</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0.0009379727685325245</v>
+        <v>-0.0004111321948134239</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.002723146747352423</v>
+        <v>-0.003328290468986417</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0.01622390891840615</v>
+        <v>-0.006356062943535945</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.0007261724659606728</v>
+        <v>-0.0005376344086021722</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.001754916792738237</v>
+        <v>-0.007745839636913754</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.005977229601518097</v>
+        <v>-0.005337858685590868</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0.001248884924174887</v>
+        <v>-0.003036053130929806</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0.003025718608169359</v>
+        <v>-0.002259887005649763</v>
       </c>
       <c r="EE5" t="n">
-        <v>-0.0002378828427000101</v>
+        <v>-0.0001226617601962299</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0.002662632375189033</v>
+        <v>-0.003358547655068112</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.001802656546489612</v>
+        <v>-0.005839636913767066</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0.0009487666034155961</v>
+        <v>-0.0009056839475327982</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.002098117864856564</v>
+        <v>-0.0005126561999359458</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.002995461422087664</v>
+        <v>-0.003055975794251165</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0.008381240544629321</v>
+        <v>-0.002508960573476715</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0.0002530044275775189</v>
+        <v>-6.325110689437974e-05</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0.00032041012495998</v>
+        <v>-6.133088009812049e-05</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0.0008028545941124454</v>
+        <v>-0.0005961251862891426</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.0005748865355521993</v>
+        <v>-0.0007168458781362297</v>
       </c>
       <c r="EQ5" t="n">
-        <v>-0.002087745839636834</v>
+        <v>-0.001121435437359852</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0.0004480286738351436</v>
+        <v>-5.961251862891536e-05</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.0003478810879190885</v>
+        <v>-0.001345722524831794</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0.002602118003025633</v>
+        <v>-0.001042624961668148</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.004165381055229911</v>
+        <v>-0.002299546142208797</v>
       </c>
       <c r="EV5" t="n">
-        <v>-0.0002810743285446615</v>
+        <v>-6.17093489663656e-05</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0.001739405439595243</v>
+        <v>-0.001374141161773901</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0.002299880525687015</v>
+        <v>-0.005295007564296561</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.005537065052950018</v>
+        <v>-0.004841149773071152</v>
       </c>
     </row>
     <row r="6">
@@ -3083,466 +3083,466 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.0009163005138896674</v>
+        <v>-0.00236883768196656</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0003993701438156999</v>
+        <v>-0.0003956340240052703</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0006238555011879143</v>
+        <v>-0.0001471318049247605</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001090420451901747</v>
+        <v>-0.001040383915650456</v>
       </c>
       <c r="F6" t="n">
-        <v>4.714016341922367e-05</v>
+        <v>-0.0002527559552845282</v>
       </c>
       <c r="G6" t="n">
-        <v>-8.292505575739073e-05</v>
+        <v>-0.001054028732042467</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0004526919677473679</v>
+        <v>-0.0006355989545559326</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.001148161062804787</v>
+        <v>-0.0007163881395069793</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.001161717194529493</v>
+        <v>-0.0007488868906322167</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0002004614325241905</v>
+        <v>-0.0004591741748590478</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0003523635159878941</v>
+        <v>-0.0005449738813902649</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0004477685864724412</v>
+        <v>-0.000565283212730927</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.003556624972478451</v>
+        <v>-0.002422108062188835</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.001592287628167194</v>
+        <v>-0.001699214243875225</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0006310212069962906</v>
+        <v>-0.001249871257521576</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.002257890319788109</v>
+        <v>-0.00395540106546943</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.001017402858301972</v>
+        <v>-0.002108476244657373</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.002575871039381791</v>
+        <v>-0.001896766489400914</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0006916895354816933</v>
+        <v>-0.0009280751472375115</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.000796567388893632</v>
+        <v>0.0002071558906545756</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001134159193282491</v>
+        <v>-0.001648100110151193</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0005052137438175536</v>
+        <v>-0.0002034033919444456</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.0001463515649086034</v>
+        <v>-0.002771577196153086</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.0003455963844093413</v>
+        <v>-0.0001758816756162407</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0002484292244232494</v>
+        <v>-0.003674870399238383</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.0004090258074245651</v>
+        <v>-0.001027982966319138</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0003734751456825502</v>
+        <v>-0.0001992448651797818</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.002255656521091609</v>
+        <v>-0.0008118887981539119</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.0008942401365462038</v>
+        <v>-0.0001665740685269757</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.003840194386195686</v>
+        <v>-0.0005476719577643008</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.001095921515678985</v>
+        <v>-0.001473401522045545</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.001009785739725669</v>
+        <v>-0.0006854370095909113</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0006000949843330329</v>
+        <v>-0.0006031344776327302</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.0001061880190253495</v>
+        <v>-0.0008682763245372399</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.002756694075479682</v>
+        <v>-0.001272624710418069</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.004532100997280198</v>
+        <v>0.00514799445081815</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.0008756319887644582</v>
+        <v>-0.001111969366738544</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.001754074240734596</v>
+        <v>-0.003961558156393546</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.002077641459921764</v>
+        <v>-0.001254041798981573</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.002761487811428326</v>
+        <v>-0.0007891146865695502</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.001198113670056966</v>
+        <v>-0.001294402354727348</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.002295718201213218</v>
+        <v>-0.003037404820203485</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.002540787362812849</v>
+        <v>0.001502839110678558</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.0008641346111615073</v>
+        <v>-0.0008285345846270609</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.001416833683565122</v>
+        <v>-0.0008029874129354631</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.0007551250751818839</v>
+        <v>-0.001590910917946337</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.0007409861744340246</v>
+        <v>-0.0009003543668371583</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.001342931942120146</v>
+        <v>-0.0007963479370265591</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.000378051924096337</v>
+        <v>-0.0002088472119844836</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.001948208808914351</v>
+        <v>-0.001062767046436794</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.0002183679983165821</v>
+        <v>-0.0003610584018553769</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.0002004244800339367</v>
+        <v>-0.002764467254957406</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.00119299179309913</v>
+        <v>-0.002508207782815288</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.875624633706554e-05</v>
+        <v>-0.0004444219918991188</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.000143399025876384</v>
+        <v>-0.0005027926971772956</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.001951033667135987</v>
+        <v>-0.0008237058298632638</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.00117677766455509</v>
+        <v>-0.002635339187649116</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.001205743515492994</v>
+        <v>-0.001216393725414797</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.0002592617322786067</v>
+        <v>-0.0005244018753904567</v>
       </c>
       <c r="BI6" t="n">
-        <v>5.775374500774648e-05</v>
+        <v>-0.002104336316805011</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.0005386031107277977</v>
+        <v>-0.00232141092571124</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.001865906845207663</v>
+        <v>-0.002642309623633474</v>
       </c>
       <c r="BL6" t="n">
-        <v>-8.513921362773855e-06</v>
+        <v>-0.0001530407521315336</v>
       </c>
       <c r="BM6" t="n">
-        <v>3.898530276445211e-05</v>
+        <v>-0.0001526000751292861</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.0002060897671199407</v>
+        <v>-0.000771859341423542</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.0005934003993343761</v>
+        <v>-0.001763518395953456</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.002185239142398712</v>
+        <v>-0.001087034479366894</v>
       </c>
       <c r="BQ6" t="n">
         <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.0004447901409364852</v>
+        <v>-0.001044518733437971</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.0003577677771759685</v>
+        <v>-0.0007196228884517985</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.0002727800608734538</v>
+        <v>-0.0002850308929007506</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.000846862042307911</v>
+        <v>-0.0005815401974452544</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.0001645526337310354</v>
+        <v>-0.0007235994563013021</v>
       </c>
       <c r="BW6" t="n">
-        <v>-3.169711938426078e-05</v>
+        <v>-2.983527252613249e-05</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.0008212468785749411</v>
+        <v>-0.002337200703102421</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.001593592544921144</v>
+        <v>-0.001901408713547634</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.003913222995291355</v>
+        <v>-0.000500197179263906</v>
       </c>
       <c r="CA6" t="n">
-        <v>-0.00040149251034802</v>
+        <v>-0.0007770765914295596</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.003279958503139332</v>
+        <v>-0.0009402025839585188</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.654382991610141e-05</v>
+        <v>-0.001778111479199249</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0.001252103440354604</v>
+        <v>-0.002355135518113791</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.0004971507949078441</v>
+        <v>-0.002523624347685932</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.0004136012396929955</v>
+        <v>-0.001350527320309103</v>
       </c>
       <c r="CG6" t="n">
-        <v>7.056488650949156e-05</v>
+        <v>-0.001720841282340826</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0006074430644234352</v>
+        <v>-0.0006854617022472254</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.0004431887642203147</v>
+        <v>-0.0003430759055269072</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-8.628608829702455e-05</v>
+        <v>-5.251653600431006e-05</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.0006432541559817622</v>
+        <v>-0.0011946117159921</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.001185407652799497</v>
+        <v>-0.001987281988796308</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0.0008290357497233336</v>
+        <v>-0.0008757784445548671</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.001263009486838313</v>
+        <v>-0.0006854577749490859</v>
       </c>
       <c r="CO6" t="n">
-        <v>-0.0007885553287164865</v>
+        <v>-0.0001513708569612415</v>
       </c>
       <c r="CP6" t="n">
-        <v>-5.25094213680688e-05</v>
+        <v>-0.0003693261353385241</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.0007909597223022591</v>
+        <v>-0.00120044093963777</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.003542851339881406</v>
+        <v>-0.007381966233159479</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0.003134712833537731</v>
+        <v>-0.003993738511220004</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0.001477793535762317</v>
+        <v>-0.002503968743810064</v>
       </c>
       <c r="CU6" t="n">
-        <v>-6.22730586657072e-05</v>
+        <v>-0.0003491529972284746</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0.0003840403379357676</v>
+        <v>0</v>
       </c>
       <c r="CW6" t="n">
         <v>0</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0.002193018161313493</v>
+        <v>-0.002757981504824003</v>
       </c>
       <c r="CY6" t="n">
-        <v>-0.004374945477389774</v>
+        <v>-0.00990009273433444</v>
       </c>
       <c r="CZ6" t="n">
-        <v>3.928346951602435e-05</v>
+        <v>-0.0005388716017898531</v>
       </c>
       <c r="DA6" t="n">
-        <v>-0.0003862694164348424</v>
+        <v>7.666360012267836e-06</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0.0009109003128806108</v>
+        <v>-0.000797396058492711</v>
       </c>
       <c r="DC6" t="n">
-        <v>-0.002202630512248139</v>
+        <v>-0.007411669468177449</v>
       </c>
       <c r="DD6" t="n">
-        <v>-0.0003396186809473539</v>
+        <v>-0.0005470081515570769</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0.0001082012949162825</v>
+        <v>-0.0003844921499519677</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.002085378962491352</v>
+        <v>-0.002115491162547683</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0.0006392322398122042</v>
+        <v>-0.0001162831885349463</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0.001312865653221318</v>
+        <v>-0.002320924271439565</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.0006359631303124447</v>
+        <v>-0.0008621604695103146</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.0008616341129412675</v>
+        <v>-0.000727246522961203</v>
       </c>
       <c r="DK6" t="n">
-        <v>1.142003345647175e-06</v>
+        <v>-0.00137167909733393</v>
       </c>
       <c r="DL6" t="n">
-        <v>-2.314100586240375e-05</v>
+        <v>-0.0002319859187026929</v>
       </c>
       <c r="DM6" t="n">
-        <v>-0.0004376193226185293</v>
+        <v>-0.001452057857415937</v>
       </c>
       <c r="DN6" t="n">
-        <v>-1.780433266228287e-05</v>
+        <v>-0.002886714522162678</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.0004018792351475009</v>
+        <v>-0.004684227258072184</v>
       </c>
       <c r="DP6" t="n">
-        <v>-0.001408102278920681</v>
+        <v>-0.00291440794251234</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0.0003141247308458189</v>
+        <v>-7.55302335124275e-05</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.0002386782680397437</v>
+        <v>-6.315171797719455e-05</v>
       </c>
       <c r="DS6" t="n">
-        <v>-8.695995578474614e-05</v>
+        <v>-5.374915628869326e-05</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0.001554884816891316</v>
+        <v>-0.0003553006629848365</v>
       </c>
       <c r="DU6" t="n">
-        <v>-8.868919865361591e-05</v>
+        <v>-0.001989774404385408</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>-7.862463982009628e-05</v>
+        <v>-0.0002142570529841431</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.0007464298245329404</v>
+        <v>-0.0006331230128062748</v>
       </c>
       <c r="DY6" t="n">
-        <v>-0.0003366093640715079</v>
+        <v>-0.003027440176851931</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-0.000207253416790748</v>
+        <v>1.490312965722884e-05</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.0004041605893114641</v>
+        <v>-0.0008945643972672252</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.0008710624762728908</v>
+        <v>-0.002794085750383662</v>
       </c>
       <c r="EC6" t="n">
-        <v>-0.0006654439035828103</v>
+        <v>-0.001693278507600857</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0.0008686162704287349</v>
+        <v>-0.0008532946713733697</v>
       </c>
       <c r="EE6" t="n">
-        <v>-0.0001263802235696887</v>
+        <v>-8.941877794337304e-05</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0.001093408867762308</v>
+        <v>-0.00019057001008983</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.001309800986282644</v>
+        <v>-0.0008649320625060242</v>
       </c>
       <c r="EH6" t="n">
-        <v>-0.0004365163809070455</v>
+        <v>-9.691973463329118e-05</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0.0008835012214832127</v>
+        <v>-0.0002292707153193713</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.001211051745647412</v>
+        <v>-0.0005614806638215009</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0.0008597579383068793</v>
+        <v>-0.0002076734122175794</v>
       </c>
       <c r="EL6" t="n">
         <v>0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0.0001171143035602756</v>
+        <v>0</v>
       </c>
       <c r="EN6" t="n">
-        <v>-2.269288956127102e-05</v>
+        <v>-7.209227811599551e-05</v>
       </c>
       <c r="EO6" t="n">
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-3.828449145278633e-05</v>
+        <v>-4.599816007359037e-05</v>
       </c>
       <c r="EQ6" t="n">
-        <v>-0.0008966645923434879</v>
+        <v>-0.0009180554186945855</v>
       </c>
       <c r="ER6" t="n">
         <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.0001358658814981123</v>
+        <v>-2.269288956127102e-05</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0.0009947140998286474</v>
+        <v>-0.0003272675495047256</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0.00137466799132219</v>
+        <v>-0.0006473799398109325</v>
       </c>
       <c r="EV6" t="n">
-        <v>-7.115749525617721e-05</v>
+        <v>-1.665334536937735e-17</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0.001104897609441044</v>
+        <v>-0.0004216740459624863</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0.0009288069992279879</v>
+        <v>-0.001312865653221329</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.0006320538533264308</v>
+        <v>-0.0007121829833631161</v>
       </c>
     </row>
     <row r="7">
@@ -3552,466 +3552,466 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002185953268455154</v>
+        <v>0.0005180630612476478</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001539395811963884</v>
+        <v>1.038647622003685e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.000111748098941572</v>
+        <v>0.0002672369143099596</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000721238316114936</v>
+        <v>0.0001885606536769113</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0002120651043723443</v>
+        <v>6.231894121854913e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0007197732718119466</v>
+        <v>0.0003380831405020601</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001930566065225569</v>
+        <v>0.000573206823013006</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00132071940856448</v>
+        <v>0.0005802026818310214</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0002215230214976771</v>
+        <v>0.001178846949309437</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001842188561116232</v>
+        <v>-0.0002025577380944332</v>
       </c>
       <c r="L7" t="n">
-        <v>-8.920606601250936e-05</v>
+        <v>-0.0003430524173517413</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0005626819163391583</v>
+        <v>0.0002125137660442645</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0004992064355657577</v>
+        <v>0.0002566719314501087</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001138546576047905</v>
+        <v>0.0005855795672673414</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0006362548766434051</v>
+        <v>0.0009333026768850672</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.003789734592796612</v>
+        <v>0.001059944643251004</v>
       </c>
       <c r="R7" t="n">
-        <v>-4.961122890859149e-05</v>
+        <v>-0.001071250786061861</v>
       </c>
       <c r="S7" t="n">
-        <v>0.000473477177907361</v>
+        <v>0.0003461241127275139</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0003582286351550834</v>
+        <v>-0.0003635401789240878</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0003128951375784172</v>
+        <v>0.0005218216318785496</v>
       </c>
       <c r="V7" t="n">
-        <v>0.003076297423518864</v>
+        <v>-0.001374047880767487</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0004465155571262702</v>
+        <v>0.0006685548897651606</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001023109513300319</v>
+        <v>-0.0002837621472915165</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.490312965722884e-05</v>
+        <v>0.0001687537025115704</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0006550106637675856</v>
+        <v>-0.0004783243706662443</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0003748631428234395</v>
+        <v>0.0002242870874719472</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.895994085931556e-05</v>
+        <v>0.0001860235232639173</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.001063112267592037</v>
+        <v>-0.0002586704913323856</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.005222141872923431</v>
+        <v>0.002597724410321062</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.005350221506460844</v>
+        <v>0.004437853208530801</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.001136091162173158</v>
+        <v>-0.0003236880315086288</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.0004183039509539299</v>
+        <v>-0.0002936915087198899</v>
       </c>
       <c r="AH7" t="n">
-        <v>5.961251862893202e-05</v>
+        <v>-0.000283437314018492</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0007936271555693652</v>
+        <v>0.0003997725135863716</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-9.615696896868038e-05</v>
+        <v>0.001456594146126983</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.007130906024312084</v>
+        <v>0.008637355973589944</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.0001749970949616208</v>
+        <v>-0.0003729541701722072</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.0005503841972963885</v>
+        <v>-0.001276302753389264</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.0001264170494095607</v>
+        <v>0.0004219241747373592</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.00101707576579837</v>
+        <v>0.0004294415026401266</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.0005350121849891365</v>
+        <v>0.0003832599036928342</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.0004974462252345158</v>
+        <v>-0.001766552030808311</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.004797315990558465</v>
+        <v>0.003638438296019087</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0007853679106050726</v>
+        <v>-7.775668088287892e-05</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.301679784660117e-05</v>
+        <v>-0.0003672686517907642</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.0003913624851846598</v>
+        <v>-0.0004749336529786097</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.0002393779683119102</v>
+        <v>-0.0002812204642170357</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.0002675341026516953</v>
+        <v>-4.260791467152744e-05</v>
       </c>
       <c r="AX7" t="n">
-        <v>2.645412954216386e-05</v>
+        <v>-7.447161126193924e-05</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.0008827326068401198</v>
+        <v>0.0003160106570647636</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.000887519342759363</v>
+        <v>-7.444474430918225e-05</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.00185474365075417</v>
+        <v>0.001852695102364155</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.002354401509630355</v>
+        <v>0.001276021981850356</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.000297637169282794</v>
+        <v>-0.0002932830369823724</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.953535824840037e-05</v>
+        <v>-0.0002535713204671553</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.0001206001494360454</v>
+        <v>-0.0003659134038836332</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.002391185244492833</v>
+        <v>-0.0003695746949538171</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.0006095927039896587</v>
+        <v>-0.0003128936934843173</v>
       </c>
       <c r="BH7" t="n">
-        <v>-6.19743144649576e-05</v>
+        <v>0.0002207726079434147</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.002676344761866112</v>
+        <v>0.001087979700331554</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.0002674854169364249</v>
+        <v>0.0007797363510990307</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.0006467435556762157</v>
+        <v>-0.001579122027868207</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0003270575979294088</v>
+        <v>-6.100101959724546e-05</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.0007122369809383355</v>
+        <v>0.0001663797515207455</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.001978205823171553</v>
+        <v>0.002356160445728184</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.001400872180274343</v>
+        <v>0.0001425982582381913</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.0001154912571504795</v>
+        <v>-0.0003091970845421621</v>
       </c>
       <c r="BQ7" t="n">
         <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.00226247016730628</v>
+        <v>0.0008602614324386082</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.0009198476398883549</v>
+        <v>7.573351541110274e-05</v>
       </c>
       <c r="BT7" t="n">
-        <v>7.906388361791361e-05</v>
+        <v>0.0001887594315112928</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.001204004173486828</v>
+        <v>0.001555376388121971</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.0003275114991364569</v>
+        <v>-0.0001632780085198904</v>
       </c>
       <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0.0004162949747249179</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0.0002110395668686704</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0.001157664003370295</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>-0.000153989520764719</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>-0.0002308125702223884</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>-0.0004483826608187302</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0.0002161719558164188</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>-0.0005916481444624977</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>-1.276185488754966e-05</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>-0.0002606562404170287</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>-1.376022567536329e-05</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.0006889259149867766</v>
+      </c>
+      <c r="CJ7" t="n">
         <v>-1.490312965722884e-05</v>
       </c>
-      <c r="BX7" t="n">
-        <v>0.0009419723606228336</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>-0.0003139005069200785</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>-0.00062745589160767</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>-3.023584968173121e-05</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>6.322427022603661e-05</v>
-      </c>
-      <c r="CC7" t="n">
-        <v>0.0006010791877313238</v>
-      </c>
-      <c r="CD7" t="n">
-        <v>0.0001593204342420606</v>
-      </c>
-      <c r="CE7" t="n">
-        <v>0.0007485058701496461</v>
-      </c>
-      <c r="CF7" t="n">
-        <v>0.0008188851664426122</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>0.0002722295123544605</v>
-      </c>
-      <c r="CH7" t="n">
-        <v>-0.0001125796351748864</v>
-      </c>
-      <c r="CI7" t="n">
-        <v>-0.0002038814521565235</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>0</v>
-      </c>
       <c r="CK7" t="n">
-        <v>0.001065323430958509</v>
+        <v>-0.0005535864135731483</v>
       </c>
       <c r="CL7" t="n">
-        <v>-0.0006771290612383573</v>
+        <v>0.0002578247811946821</v>
       </c>
       <c r="CM7" t="n">
-        <v>-0.0003177057797658034</v>
+        <v>-0.0002010945093412708</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0001375862262534389</v>
+        <v>-9.435648865401821e-05</v>
       </c>
       <c r="CO7" t="n">
-        <v>-0.0001403947637161007</v>
+        <v>0.0005096756866910024</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.0001072638292823225</v>
+        <v>-1.533272002453012e-05</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.00106285216973882</v>
+        <v>-0.0001652358746315641</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0.0005383483107657184</v>
+        <v>-0.001389883970022532</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0.0006105647358207677</v>
+        <v>-0.0009969143475527075</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0.0006579011939034153</v>
+        <v>-0.0007733574264979171</v>
       </c>
       <c r="CU7" t="n">
-        <v>9.138393919616016e-05</v>
+        <v>-3.162555344718987e-05</v>
       </c>
       <c r="CV7" t="n">
-        <v>-0.0001371976184273871</v>
+        <v>3.071590638081823e-05</v>
       </c>
       <c r="CW7" t="n">
         <v>0</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0.0005263978489371656</v>
+        <v>-0.001262112703347623</v>
       </c>
       <c r="CY7" t="n">
-        <v>-0.0008906403996745471</v>
+        <v>-0.0008311784022883517</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.0002014609953102153</v>
+        <v>-0.000168168907746008</v>
       </c>
       <c r="DA7" t="n">
-        <v>3.114072504797893e-05</v>
+        <v>6.109905920508308e-05</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.0001536758840144092</v>
+        <v>0.0001335481836466146</v>
       </c>
       <c r="DC7" t="n">
-        <v>-0.001171185558194054</v>
+        <v>-0.001799054613710543</v>
       </c>
       <c r="DD7" t="n">
-        <v>-0.0001652358746315974</v>
+        <v>-0.0003296980624334533</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.001441199066590709</v>
+        <v>0.0004752750800714467</v>
       </c>
       <c r="DF7" t="n">
-        <v>9.087289435152912e-05</v>
+        <v>-1.609405558826715e-05</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.0001955184479850547</v>
+        <v>0.0003576012417286778</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.0005737315501148476</v>
+        <v>-0.0008683261124576957</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.0004272852136431193</v>
+        <v>-0.0001084710435173497</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.00101726038829858</v>
+        <v>0.0004726508587608813</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.0003386171945049421</v>
+        <v>-0.0004492168940939678</v>
       </c>
       <c r="DL7" t="n">
-        <v>6.200784108796875e-05</v>
+        <v>-0.0001245819869924947</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.0001240373326431621</v>
+        <v>-0.0005973715651135192</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.0004326581521187478</v>
+        <v>-0.00153280547966394</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.0003788184291258267</v>
+        <v>-0.0009147225748486088</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.0002982861138021764</v>
+        <v>-0.001047145288870915</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.0001194743130226994</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.07715582450952e-05</v>
+        <v>-3.08546744831828e-05</v>
       </c>
       <c r="DS7" t="n">
-        <v>1.561524047470342e-05</v>
+        <v>0</v>
       </c>
       <c r="DT7" t="n">
-        <v>-0.0006533822704301529</v>
+        <v>9.237698792908256e-05</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.0003357020714512549</v>
+        <v>-0.0008047767036289788</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.000140929753599156</v>
+        <v>-0.0001199850828383919</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.0002833379251013346</v>
+        <v>-0.0004224427148100285</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.0007940432746445015</v>
+        <v>-0.0003982211302705152</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-7.790756517199738e-05</v>
+        <v>7.751249267418103e-05</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.0002771190422422798</v>
+        <v>0.0001851879329844819</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0.0002354930901556918</v>
+        <v>-0.001749346745174796</v>
       </c>
       <c r="EC7" t="n">
-        <v>-0.0005113476493628033</v>
+        <v>-0.0008492530731669667</v>
       </c>
       <c r="ED7" t="n">
-        <v>1.685539115204859e-05</v>
+        <v>-0.0001092492669679424</v>
       </c>
       <c r="EE7" t="n">
-        <v>-6.217844144863482e-05</v>
+        <v>0</v>
       </c>
       <c r="EF7" t="n">
-        <v>-0.0008364113419300657</v>
+        <v>9.157792722203073e-05</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.0001090241628727451</v>
+        <v>9.1035347724644e-06</v>
       </c>
       <c r="EH7" t="n">
-        <v>1.457138446078754e-05</v>
+        <v>3.066544004907134e-05</v>
       </c>
       <c r="EI7" t="n">
-        <v>-0.000387444717954083</v>
+        <v>0.0003751059634130194</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.0003733572281959641</v>
+        <v>-0.0001300637336699217</v>
       </c>
       <c r="EK7" t="n">
-        <v>-6.39641877637154e-05</v>
+        <v>1.490312965723439e-05</v>
       </c>
       <c r="EL7" t="n">
         <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.0001105900481479405</v>
+        <v>1.486767766873953e-05</v>
       </c>
       <c r="EN7" t="n">
-        <v>1.581277672358938e-05</v>
+        <v>7.827249703692973e-05</v>
       </c>
       <c r="EO7" t="n">
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>7.888673392010824e-05</v>
+        <v>3.08546744831828e-05</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-3.540594966660594e-05</v>
+        <v>-0.000615575837976967</v>
       </c>
       <c r="ER7" t="n">
         <v>0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-3.123048094940684e-05</v>
+        <v>0</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0.0002551417619551632</v>
+        <v>9.018676347951615e-05</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0.0003820605553121692</v>
+        <v>0.0001855863638811794</v>
       </c>
       <c r="EV7" t="n">
-        <v>6.247288344377044e-05</v>
+        <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.0002886819745664349</v>
+        <v>-0.0001189414213500051</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.0001881193576352025</v>
+        <v>-0.0007796623284593573</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.0004138326786306878</v>
+        <v>-0.0003176835910610687</v>
       </c>
     </row>
     <row r="8">
@@ -4021,466 +4021,466 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002761018334670848</v>
+        <v>0.001615444751354267</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0008448320829946953</v>
+        <v>0.0002849876576904608</v>
       </c>
       <c r="D8" t="n">
-        <v>0.000230874427727365</v>
+        <v>0.0003640120776681772</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00243288874906</v>
+        <v>0.000957469751153131</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0005332480281906249</v>
+        <v>0.000550753158981096</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001588209400150198</v>
+        <v>0.00115048815650099</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001835611364986003</v>
+        <v>0.0009209163209536464</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002118711356941758</v>
+        <v>0.002102548851536818</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0007622180988466787</v>
+        <v>0.002330853937539346</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0007779719379033184</v>
+        <v>9.631683043875017e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001149954001840175</v>
+        <v>6.925278785825385e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001249589326566666</v>
+        <v>0.002444691564291091</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003950545845277248</v>
+        <v>0.00175633904136277</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001425492364149145</v>
+        <v>0.001193929663661211</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001200755336988848</v>
+        <v>0.001229140099697851</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.005891699170978734</v>
+        <v>0.005081974726013713</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001327708773456662</v>
+        <v>-0.0004611993496332872</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001856878090463102</v>
+        <v>0.003473209025058022</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0007908177964766506</v>
+        <v>-2.401546945872413e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>0.002607134563311278</v>
+        <v>0.0008751913698855446</v>
       </c>
       <c r="V8" t="n">
-        <v>0.003436448937480971</v>
+        <v>0.0004171691236682734</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0009300958032648854</v>
+        <v>0.001056470110793192</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001593149607012401</v>
+        <v>0.001630952975330335</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.687242602474111e-05</v>
+        <v>0.0003005549810057378</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.003182862321110122</v>
+        <v>0.001234746638900197</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.005016726833864363</v>
+        <v>0.002247802941726396</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0005388510295324834</v>
+        <v>0.0005115110627542302</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0007075973168162691</v>
+        <v>0.0009497560825323409</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.007711519180996027</v>
+        <v>0.004704090374585796</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.00889947774464466</v>
+        <v>0.005464600935659045</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.002996974330632843</v>
+        <v>0.00138896705021746</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0004320690910104397</v>
+        <v>6.720430107526321e-05</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0008496477505468197</v>
+        <v>0.0004075918166177806</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.001079310551754928</v>
+        <v>0.001843835161722787</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.004989955200875829</v>
+        <v>0.006076132897500572</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.01862362304200979</v>
+        <v>0.01715596813671536</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.000679159254118883</v>
+        <v>0.0003379913970586096</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.003322288093976606</v>
+        <v>-0.0001257461648965119</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.0002981737005399193</v>
+        <v>0.001409085895221582</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.002964363616949153</v>
+        <v>0.001576763184918406</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0001871010308467591</v>
+        <v>0.0008262634281648363</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.001356020274837305</v>
+        <v>0.0002214106124059922</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.006174630210298302</v>
+        <v>0.007789348470918602</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.001974115173761304</v>
+        <v>0.0009855872676960171</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.002164608315876651</v>
+        <v>0.0004395941907976292</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.001989750159097564</v>
+        <v>0.0005876668902441457</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.628201172472146e-05</v>
+        <v>0.0002427033963260883</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.00135596701265783</v>
+        <v>0.001313351494281503</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0007029450214692755</v>
+        <v>6.290262489150044e-05</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.001707163507226323</v>
+        <v>0.0008346336243654745</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.003416877503689611</v>
+        <v>0.0008090836502300441</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.003192555995165658</v>
+        <v>0.003706022502701837</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.004096443575111464</v>
+        <v>0.00258130727919364</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.000730558426702399</v>
+        <v>0.0002977764084437673</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0003248527252553646</v>
+        <v>0.0002901486194831632</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.001872626344185391</v>
+        <v>0.0006287808149206681</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.004165712825923218</v>
+        <v>0.00249919972494822</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.001291955703487113</v>
+        <v>0.002548487666228114</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.0007817423766166482</v>
+        <v>0.001193408955293335</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.005978878260916694</v>
+        <v>0.007812883631101298</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.003410153664642712</v>
+        <v>0.002470242983955357</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.0008717625904411135</v>
+        <v>-0.0002281536575148124</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0004449333673139211</v>
+        <v>0.0002666042389601303</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0008955899556110924</v>
+        <v>0.0004837205416045487</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.003168570216873087</v>
+        <v>0.00309758917031302</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.003258223348758793</v>
+        <v>0.001257861160963425</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0006533227234994027</v>
+        <v>0.001092614774704798</v>
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.003637167953352247</v>
+        <v>0.004216514674924665</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.001278576646710919</v>
+        <v>0.0004315460635466478</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0012515200209088</v>
+        <v>0.0004718386507238271</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.002261074647263756</v>
+        <v>0.003328784610016836</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.001518647613617793</v>
+        <v>0.000843745187102618</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.319339935989376e-05</v>
+        <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.001686735505896467</v>
+        <v>0.00162310648837663</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.001462682592009254</v>
+        <v>0.001473105011865347</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.002457874453554407</v>
+        <v>0.002119070815233687</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.0006974088891467833</v>
+        <v>0.0002826276836601166</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.001482098251048075</v>
+        <v>0.000768397225234535</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.0009172074871922148</v>
+        <v>0.0008315827120934289</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.002244770914253452</v>
+        <v>0.001550817803925508</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.001519813576692175</v>
+        <v>-0.0001067587404067705</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.001710589398084031</v>
+        <v>0.0007247201541577292</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.001179197818202626</v>
+        <v>0.0005905811146074885</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0003217334928245941</v>
+        <v>0.0004148314987633739</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.001026449056295117</v>
+        <v>0.001085618349157383</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.40307593719985e-05</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.002642107217067549</v>
+        <v>0.0004725847923123444</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.0006797266739593744</v>
+        <v>0.000493494254065674</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.001688864352107072</v>
+        <v>0.0004872103178466452</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0005617353593743241</v>
+        <v>0.001004134148482788</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.002566481127481021</v>
+        <v>0.001635888445077635</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.000365407738384993</v>
+        <v>0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.001743608762550985</v>
+        <v>0.0008274664849342056</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.002275917816752537</v>
+        <v>0.002193973942278424</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0.0001137706382818626</v>
+        <v>-1.271342025738198e-06</v>
       </c>
       <c r="CT8" t="n">
-        <v>-3.953194180902898e-05</v>
+        <v>-3.828648825431325e-05</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.0003860427520285454</v>
+        <v>3.128375033041031e-05</v>
       </c>
       <c r="CV8" t="n">
-        <v>9.581144320137958e-05</v>
+        <v>0.000104473412435771</v>
       </c>
       <c r="CW8" t="n">
         <v>0</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.0003604613905799636</v>
+        <v>3.616405916199159e-05</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.001558935756963206</v>
+        <v>0.001885904703520863</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.0003166843527454777</v>
+        <v>0.0001561106155218317</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0001436327219059646</v>
+        <v>0.000433796478109183</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.001257151406247792</v>
+        <v>0.0009277359085399313</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.001231375949236077</v>
+        <v>-0.0001927711859088216</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.0002622174244985259</v>
+        <v>-3.127955461526277e-05</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.002190272638525317</v>
+        <v>0.001191099322565475</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.0009959087214863743</v>
+        <v>0.0005103758614362963</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.0007556809606936998</v>
+        <v>0.0006813736943471454</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.0004918032786885517</v>
+        <v>0.0003509191300055836</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.001496913682827908</v>
+        <v>0.0006706408345752729</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.001519192732337524</v>
+        <v>0.0007463717022151455</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.001029196597082033</v>
+        <v>0.0003958623652366905</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.0002535346584910586</v>
+        <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.0007200680918062474</v>
+        <v>0.0004003059528472297</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.00120894787087211</v>
+        <v>-6.108303616623458e-05</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.0009222596818929368</v>
+        <v>3.85968219350773e-06</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.000524865234191349</v>
+        <v>-0.0003480386600859337</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.0004047913296829631</v>
+        <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0003083626012430896</v>
+        <v>2.983527252612972e-05</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.0002531318062304055</v>
+        <v>0.0001102093803661025</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.0012355851328402</v>
+        <v>0.0006344927707426034</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.0009155325176056689</v>
+        <v>0.0003180066443333351</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0004862181887818118</v>
+        <v>0.0002860079067572463</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.0006386516728431102</v>
+        <v>4.512569327876637e-05</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.001895669935914424</v>
+        <v>0.0001940273724996528</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.0002829509180619888</v>
+        <v>0.0002879535852353205</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.001701133494573856</v>
+        <v>0.0005025444784857808</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.001346233868791274</v>
+        <v>-0.001027750095382909</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0003504126859440876</v>
+        <v>-0.0003303442052029537</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.0004414785626761786</v>
+        <v>3.883044689616255e-05</v>
       </c>
       <c r="EE8" t="n">
-        <v>2.31410058623871e-05</v>
+        <v>0</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.000723363911941316</v>
+        <v>0.0003691272839344423</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.0002693474409063173</v>
+        <v>0.0004850995841490819</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.0004872348555739259</v>
+        <v>0.0004997057702844032</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.0001588252983394184</v>
+        <v>0.0009022781256808083</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0001000065732712135</v>
+        <v>0.0007921776950768816</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.001078379219525716</v>
+        <v>0.0006711381856946725</v>
       </c>
       <c r="EL8" t="n">
         <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.0002130304320982268</v>
+        <v>8.199837258536791e-05</v>
       </c>
       <c r="EN8" t="n">
-        <v>6.34888559855884e-05</v>
+        <v>0.0001224326017052246</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.0004264977214096383</v>
+        <v>0.0002580023335992637</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.0007661913965607559</v>
+        <v>-0.0003794920941934899</v>
       </c>
       <c r="ER8" t="n">
         <v>0</v>
       </c>
       <c r="ES8" t="n">
-        <v>8.223726953388854e-05</v>
+        <v>0.0001255421003906493</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.0004045836500914418</v>
+        <v>0.0003860639915410135</v>
       </c>
       <c r="EU8" t="n">
-        <v>-4.530059653994611e-05</v>
+        <v>0.001011465431498698</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.0001741794325350571</v>
+        <v>0.0002760639540674709</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.0005496679722562154</v>
+        <v>0.0002322998121334685</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.00117459498155201</v>
+        <v>-7.611098776794096e-06</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.0003781472078756093</v>
+        <v>-0.0002234307356593829</v>
       </c>
     </row>
     <row r="9">
@@ -4490,466 +4490,466 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.007719821162444141</v>
+        <v>0.003645505971087348</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002116244411326418</v>
+        <v>0.0004996876951905094</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003106332138590173</v>
+        <v>0.00253353204172877</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003576751117734778</v>
+        <v>0.002378828426999679</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001403823178016694</v>
+        <v>0.002178788849727609</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00521609538002984</v>
+        <v>0.002593144560357685</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005096870342771997</v>
+        <v>0.002450832072617271</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003568242640499508</v>
+        <v>0.004590163934426239</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004351713859910622</v>
+        <v>0.004311626523936929</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001219149568837286</v>
+        <v>0.0008472012102874515</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0008330663248958925</v>
+        <v>0.0006285355122564229</v>
       </c>
       <c r="M9" t="n">
-        <v>0.003405017921146947</v>
+        <v>0.004241338112305815</v>
       </c>
       <c r="N9" t="n">
-        <v>0.009925484351713898</v>
+        <v>0.01259211791092596</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003328290468986417</v>
+        <v>0.003099850968703422</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002437519284171541</v>
+        <v>0.002042740414833433</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01078986587183314</v>
+        <v>0.01158650843222983</v>
       </c>
       <c r="R9" t="n">
-        <v>0.00352449223416963</v>
+        <v>-1.110223024625157e-17</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0063785394932936</v>
+        <v>0.004613905799423235</v>
       </c>
       <c r="T9" t="n">
-        <v>0.002593295382669147</v>
+        <v>0.0003771213073538449</v>
       </c>
       <c r="U9" t="n">
-        <v>0.003449301219149536</v>
+        <v>0.002378828426999669</v>
       </c>
       <c r="V9" t="n">
-        <v>0.004778972520907965</v>
+        <v>0.003903177004538594</v>
       </c>
       <c r="W9" t="n">
-        <v>0.00351713859910584</v>
+        <v>0.003993948562783689</v>
       </c>
       <c r="X9" t="n">
-        <v>0.004808296668761791</v>
+        <v>0.004091193004372296</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001642771804062104</v>
+        <v>0.0006571087216248439</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.00478739220933685</v>
+        <v>0.006631049654305454</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01141622955877811</v>
+        <v>0.01325264750378217</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001030605871330381</v>
+        <v>0.0009932713873757938</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.007682813946312816</v>
+        <v>0.004024205748865384</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.01589015735883984</v>
+        <v>0.009137670196671688</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.02393442622950821</v>
+        <v>0.02011922503725782</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.01096870342771986</v>
+        <v>0.00251456608402334</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.003300624442462053</v>
+        <v>0.00240856378233717</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.002497769848349663</v>
+        <v>0.001486767766874764</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.002622950819672165</v>
+        <v>0.00514372163388801</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.0122807017543859</v>
+        <v>0.01153502235469447</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0221845109534094</v>
+        <v>0.0208886146251157</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.001172477630360946</v>
+        <v>0.001633888048411514</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.01427719821162448</v>
+        <v>0.01803278688524591</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.00205748865355524</v>
+        <v>0.00187382885696441</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.004072817031780284</v>
+        <v>0.00481089258698939</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.002831594634873347</v>
+        <v>0.002692889561270828</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.002541603630862354</v>
+        <v>0.004659055846960814</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.01451564828614013</v>
+        <v>0.02345752608047687</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.002514142049025769</v>
+        <v>0.002755527074655539</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.005292893250074282</v>
+        <v>0.004838192886895187</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.004288799753162586</v>
+        <v>0.001419315026226475</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.0007153502235469622</v>
+        <v>0.0004936747917309358</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.006726319037334128</v>
+        <v>0.003116322122801607</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.001159678858162305</v>
+        <v>0.001132637853949337</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.005484351713859947</v>
+        <v>0.003091817613991277</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.007957639939485695</v>
+        <v>0.00178013741411619</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.01323223312518581</v>
+        <v>0.0079273827534039</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.01350223546944862</v>
+        <v>0.008166915052160939</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.001433691756272348</v>
+        <v>0.001194743130226961</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.001672640382317758</v>
+        <v>0.000754242614707723</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.002444113263785441</v>
+        <v>0.003904619970193723</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.007655068078668737</v>
+        <v>0.006481481481481454</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.00265459088069947</v>
+        <v>0.006928895612707975</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.001100208147487325</v>
+        <v>0.002658303464755063</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.01675111773472434</v>
+        <v>0.01332339791356183</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.007600596125186321</v>
+        <v>0.00279512340172462</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.006125483199524185</v>
+        <v>0.006632489586670886</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.002712369597615538</v>
+        <v>0.0006541778174248946</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.00203640851589012</v>
+        <v>0.002354694485842035</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.005854241338112276</v>
+        <v>0.008333333333333304</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.005573770491803287</v>
+        <v>0.008411497730711015</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.003771213073538659</v>
+        <v>0.003780839474527353</v>
       </c>
       <c r="BQ9" t="n">
         <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.007919547454431176</v>
+        <v>0.006720190306274154</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.003375149342891259</v>
+        <v>0.001634091637295709</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.002771982116244443</v>
+        <v>0.002118003025718629</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.006232980332829108</v>
+        <v>0.006807866868381196</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.00446030330062439</v>
+        <v>0.002482715273412928</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0002090800477897336</v>
+        <v>0.0002682563338301192</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.004351713859910611</v>
+        <v>0.004357034795764003</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.002349093071662156</v>
+        <v>0.001962588163140178</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.007077014570324047</v>
+        <v>0.003419565863812035</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.002375809935205142</v>
+        <v>0.001164874551971284</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.005619982158786752</v>
+        <v>0.003394091766184748</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.005084745762711807</v>
+        <v>0.002586975914362144</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.003368107302533574</v>
+        <v>0.001903062741599737</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.01082999074359762</v>
+        <v>0.002527505203687152</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.002354694485842068</v>
+        <v>0.002652757078986579</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.002199874292897552</v>
+        <v>0.002105593966059072</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.001162790697674409</v>
+        <v>0.0005352363960749007</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.002527505203687152</v>
+        <v>0.004148334380892493</v>
       </c>
       <c r="CJ9" t="n">
-        <v>8.92060660124705e-05</v>
+        <v>0.0005971087366435701</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.003795124961431606</v>
+        <v>0.0006354009077155886</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.00375558867362149</v>
+        <v>0.001313681512335774</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.002950819672131189</v>
+        <v>0.003023758099352036</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.004649776453055166</v>
+        <v>0.002950819672131155</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.003092476955099566</v>
+        <v>0.004649776453055143</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.0004399748585794727</v>
+        <v>0.0006408202499198712</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.009716840536512717</v>
+        <v>0.006080476900149035</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.009687034277198248</v>
+        <v>0.004460303300624424</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.003487332339791405</v>
+        <v>0.004274041483343783</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.002530083307621067</v>
+        <v>0.0008643815201192396</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.0008170961659333508</v>
+        <v>0.0002973535533749461</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0004769001490313229</v>
+        <v>0.0002828409805153753</v>
       </c>
       <c r="CW9" t="n">
         <v>0</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.001070472792149835</v>
+        <v>0.001089258698941009</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.004679582712369634</v>
+        <v>0.003842662632375216</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0004757656853999093</v>
+        <v>0.0005376344086021612</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.0007153502235469844</v>
+        <v>0.0008623253047873481</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.007809239940387513</v>
+        <v>0.009776453055141576</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.003397913561848021</v>
+        <v>0.001124297314178646</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.0005767382249279418</v>
+        <v>0.0001792114695340352</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.003330359797799531</v>
+        <v>0.005514157973174361</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.002056631892697502</v>
+        <v>0.001717676452217376</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.003099850968703455</v>
+        <v>0.002602118003025744</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.01058315334773214</v>
+        <v>0.003040238450074517</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.002688172043010728</v>
+        <v>0.003909003524511357</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.002538829151732347</v>
+        <v>0.00118675827607746</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.003494623655913942</v>
+        <v>0.001192250372578241</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0004480286738351213</v>
+        <v>0.000302571860816947</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.003524492234169618</v>
+        <v>0.002086438152011916</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.01342178340018509</v>
+        <v>0.002966895690193649</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.006325208269052729</v>
+        <v>0.001537968599807738</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.003645505971087371</v>
+        <v>0.0009932713873757938</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0007153502235469844</v>
+        <v>0.0001784121320249521</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.001486767766874764</v>
+        <v>0.0002723146747352523</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0007451564828614421</v>
+        <v>0.0007542426147077342</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.002479091995220994</v>
+        <v>0.004350509102128963</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.00527614933662447</v>
+        <v>0.003904619970193735</v>
       </c>
       <c r="DV9" t="n">
         <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.0008022215365627528</v>
+        <v>0.0007369432874078541</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.001639344262295128</v>
+        <v>0.001979886863607783</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.005924097500771353</v>
+        <v>0.001821983273596151</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0004470938897168764</v>
+        <v>0.0008325899494498578</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.002943800178412093</v>
+        <v>0.001967213114754107</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.004165381055229822</v>
+        <v>0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.001141622955877797</v>
+        <v>0.0007564296520423675</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.002771982116244431</v>
+        <v>0.0007807620237351709</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0001581277672358827</v>
+        <v>0.000187382885696441</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.001281640499839809</v>
+        <v>0.0004460303300623969</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.003427719821162467</v>
+        <v>0.001102831594634879</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.0009557945041815729</v>
+        <v>0.0007168458781361742</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.004569892473118242</v>
+        <v>0.001430700447093913</v>
       </c>
       <c r="EJ9" t="n">
+        <v>0.002011313639220602</v>
+      </c>
+      <c r="EK9" t="n">
         <v>0.001319924575738496</v>
       </c>
-      <c r="EK9" t="n">
-        <v>0.002616711269699634</v>
-      </c>
       <c r="EL9" t="n">
-        <v>5.973715651135248e-05</v>
+        <v>0.0002973535533749017</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.001523297491039377</v>
+        <v>0.0002563280999679174</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.0005961251862891537</v>
+        <v>0.0004599816007360147</v>
       </c>
       <c r="EO9" t="n">
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.0007153502235469844</v>
+        <v>0.000834575260804793</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.004292101341281718</v>
+        <v>0.000308546744831828</v>
       </c>
       <c r="ER9" t="n">
-        <v>2.980625931445768e-05</v>
+        <v>0.0006571087216248328</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0004769001490313229</v>
+        <v>0.0002514142049025558</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.002146050670640853</v>
+        <v>0.0008941877794336972</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.001341281669150551</v>
+        <v>0.001561524047470342</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0004778972520907865</v>
+        <v>0.0009506286415210563</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.003003270889087084</v>
+        <v>0.0007153502235469622</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.004292101341281706</v>
+        <v>0.001374141161773901</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.002652757078986634</v>
+        <v>0.00113136392206159</v>
       </c>
     </row>
   </sheetData>
